--- a/psychopy_exp_files/sequences/learning_block3_fixed-middle-10_24.xlsx
+++ b/psychopy_exp_files/sequences/learning_block3_fixed-middle-10_24.xlsx
@@ -574,12 +574,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_06.jpg</t>
+          <t>stimuli/hammer/hammer_44.jpg</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_07.jpg</t>
+          <t>stimuli/lamp/lamp_22.jpg</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -594,12 +594,12 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -609,19 +609,19 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>0.58</v>
+        <v>0.47</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.31</v>
+        <v>0.2</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
@@ -638,10 +638,10 @@
         <v>13</v>
       </c>
       <c r="V2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="W2" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3">
@@ -673,7 +673,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>stimuli/house/house_06.jpg</t>
+          <t>stimuli/hand/hand_19.jpg</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -703,28 +703,28 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0.8</v>
+        <v>0.42</v>
       </c>
       <c r="Q3" t="n">
         <v>0.31</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S3" t="n">
@@ -737,7 +737,7 @@
         <v>5</v>
       </c>
       <c r="V3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W3" t="n">
         <v>17</v>
@@ -772,12 +772,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_17.jpg</t>
+          <t>stimuli/jacket/jacket_18.jpg</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_22.jpg</t>
+          <t>stimuli/bread/bread_07.jpg</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -792,38 +792,38 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>lamp</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0.64</v>
+        <v>0.53</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.31</v>
+        <v>0.42</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S4" t="n">
@@ -836,10 +836,10 @@
         <v>9</v>
       </c>
       <c r="V4" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="W4" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -871,12 +871,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_44.jpg</t>
+          <t>stimuli/chair/chair_06.jpg</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_19.jpg</t>
+          <t>stimuli/phone/phone_23.jpg</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -891,12 +891,12 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -906,19 +906,19 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0.64</v>
+        <v>0.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.53</v>
+        <v>0.42</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
@@ -935,10 +935,10 @@
         <v>6</v>
       </c>
       <c r="V5" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="W5" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6">
@@ -970,12 +970,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_18.jpg</t>
+          <t>stimuli/bicycle/bicycle_17.jpg</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>stimuli/phone/phone_23.jpg</t>
+          <t>stimuli/lamp/lamp_22.jpg</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -990,22 +990,22 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1014,14 +1014,14 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0.64</v>
+        <v>0.75</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.47</v>
+        <v>0.42</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S6" t="n">
@@ -1034,10 +1034,10 @@
         <v>4</v>
       </c>
       <c r="V6" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="W6" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -1168,7 +1168,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_07.jpg</t>
+          <t>stimuli/dog/dog_42.jpg</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1198,28 +1198,28 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0.64</v>
+        <v>0.33</v>
       </c>
       <c r="Q8" t="n">
         <v>0.2</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S8" t="n">
@@ -1232,7 +1232,7 @@
         <v>2</v>
       </c>
       <c r="V8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="W8" t="n">
         <v>6</v>
@@ -1267,14 +1267,14 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
+          <t>stimuli/jacket/jacket_18.jpg</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
           <t>stimuli/guitar/guitar_07.jpg</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>stimuli/house/house_06.jpg</t>
-        </is>
-      </c>
       <c r="I9" t="inlineStr">
         <is>
           <t>bicycle</t>
@@ -1287,14 +1287,14 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
+          <t>jacket</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
           <t>guitar</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>house</t>
-        </is>
-      </c>
       <c r="M9" t="inlineStr">
         <is>
           <t>right</t>
@@ -1302,19 +1302,19 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P9" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="Q9" t="n">
         <v>0.47</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0.33</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
@@ -1331,10 +1331,10 @@
         <v>7</v>
       </c>
       <c r="V9" t="n">
+        <v>10</v>
+      </c>
+      <c r="W9" t="n">
         <v>13</v>
-      </c>
-      <c r="W9" t="n">
-        <v>9</v>
       </c>
     </row>
     <row r="10">
@@ -1366,12 +1366,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_19.jpg</t>
+          <t>stimuli/phone/phone_23.jpg</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_06.jpg</t>
+          <t>stimuli/ball/ball_06.jpg</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1386,38 +1386,38 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0.8</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.27</v>
+        <v>0.2</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S10" t="n">
@@ -1430,10 +1430,10 @@
         <v>10</v>
       </c>
       <c r="V10" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="W10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_07.jpg</t>
+          <t>stimuli/fish/fish_37.jpg</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_22.jpg</t>
+          <t>stimuli/house/house_06.jpg</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1485,22 +1485,22 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>fish</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>lamp</t>
+          <t>house</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1509,14 +1509,14 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.47</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S11" t="n">
@@ -1529,10 +1529,10 @@
         <v>8</v>
       </c>
       <c r="V11" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="W11" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>stimuli/fish/fish_37.jpg</t>
+          <t>stimuli/dog/dog_42.jpg</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_49.jpg</t>
+          <t>stimuli/chair/chair_06.jpg</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1584,38 +1584,38 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>fish</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0.73</v>
+        <v>0.6</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.47</v>
+        <v>0.4</v>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S12" t="n">
@@ -1628,10 +1628,10 @@
         <v>3</v>
       </c>
       <c r="V12" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="W12" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13">
@@ -1663,12 +1663,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_06.jpg</t>
+          <t>stimuli/fish/fish_37.jpg</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_44.jpg</t>
+          <t>stimuli/bicycle/bicycle_17.jpg</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1683,38 +1683,38 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>fish</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0.47</v>
+        <v>0.8</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S13" t="n">
@@ -1727,10 +1727,10 @@
         <v>17</v>
       </c>
       <c r="V13" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="W13" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_06.jpg</t>
+          <t>stimuli/ball/ball_06.jpg</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1787,17 +1787,17 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1809,11 +1809,11 @@
         <v>0.8</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.53</v>
+        <v>0.47</v>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S14" t="n">
@@ -1829,7 +1829,7 @@
         <v>13</v>
       </c>
       <c r="W14" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1861,12 +1861,12 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_34.jpg</t>
+          <t>stimuli/bicycle/bicycle_22.jpg</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_36.jpg</t>
+          <t>stimuli/guitar/guitar_12.jpg</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1881,22 +1881,22 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>guitar</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1905,14 +1905,14 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.36</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.31</v>
+        <v>0.2</v>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S15" t="n">
@@ -1925,10 +1925,10 @@
         <v>16</v>
       </c>
       <c r="V15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W15" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_19.jpg</t>
+          <t>stimuli/bread/bread_34.jpg</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_12.jpg</t>
+          <t>stimuli/lamp/lamp_13.jpg</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1980,22 +1980,22 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -2004,14 +2004,14 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0.47</v>
+        <v>0.75</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S16" t="n">
@@ -2024,10 +2024,10 @@
         <v>10</v>
       </c>
       <c r="V16" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="W16" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17">
@@ -2059,12 +2059,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_13.jpg</t>
+          <t>stimuli/hand/hand_34.jpg</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_22.jpg</t>
+          <t>stimuli/flower/flower_36.jpg</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2079,38 +2079,38 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0.58</v>
+        <v>0.64</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.47</v>
+        <v>0.42</v>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S17" t="n">
@@ -2123,10 +2123,10 @@
         <v>1</v>
       </c>
       <c r="V17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18">
@@ -2158,7 +2158,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_22.jpg</t>
+          <t>stimuli/dog/dog_19.jpg</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2178,7 +2178,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2188,12 +2188,12 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -2202,14 +2202,14 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0.53</v>
+        <v>0.58</v>
       </c>
       <c r="Q18" t="n">
         <v>0.42</v>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S18" t="n">
@@ -2222,7 +2222,7 @@
         <v>3</v>
       </c>
       <c r="V18" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="W18" t="n">
         <v>14</v>
@@ -2257,12 +2257,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_34.jpg</t>
+          <t>stimuli/house/house_48.jpg</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_12.jpg</t>
+          <t>stimuli/flower/flower_36.jpg</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2277,22 +2277,22 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -2301,14 +2301,14 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.42</v>
+        <v>0.53</v>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S19" t="n">
@@ -2321,10 +2321,10 @@
         <v>4</v>
       </c>
       <c r="V19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W19" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
@@ -2361,7 +2361,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_12.jpg</t>
+          <t>stimuli/guitar/guitar_12.jpg</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2381,7 +2381,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>guitar</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2391,19 +2391,19 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P20" t="n">
         <v>0.75</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.27</v>
+        <v>0.47</v>
       </c>
       <c r="R20" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>7</v>
       </c>
       <c r="W20" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="21">
@@ -2460,7 +2460,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_34.jpg</t>
+          <t>stimuli/ball/ball_11.jpg</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2480,17 +2480,17 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -2502,11 +2502,11 @@
         <v>0.4</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S21" t="n">
@@ -2522,7 +2522,7 @@
         <v>16</v>
       </c>
       <c r="W21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -2584,7 +2584,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2594,7 +2594,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P22" t="n">
@@ -2605,7 +2605,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S22" t="n">
@@ -2653,12 +2653,12 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_12.jpg</t>
+          <t>stimuli/car/car_34.jpg</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>stimuli/house/house_48.jpg</t>
+          <t>stimuli/bread/bread_34.jpg</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2673,12 +2673,12 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>car</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2697,10 +2697,10 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0.47</v>
+        <v>0.6</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="R23" t="inlineStr">
         <is>
@@ -2717,10 +2717,10 @@
         <v>5</v>
       </c>
       <c r="V23" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="W23" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
@@ -2752,12 +2752,12 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>stimuli/car/car_34.jpg</t>
+          <t>stimuli/jacket/jacket_12.jpg</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_34.jpg</t>
+          <t>stimuli/chair/chair_49.jpg</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2772,12 +2772,12 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2796,10 +2796,10 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0.67</v>
+        <v>0.53</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="R24" t="inlineStr">
         <is>
@@ -2816,10 +2816,10 @@
         <v>2</v>
       </c>
       <c r="V24" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="W24" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="25">
@@ -2851,14 +2851,14 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
+          <t>stimuli/car/car_34.jpg</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
           <t>stimuli/ball/ball_11.jpg</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>stimuli/chair/chair_49.jpg</t>
-        </is>
-      </c>
       <c r="I25" t="inlineStr">
         <is>
           <t>bicycle</t>
@@ -2871,14 +2871,14 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
+          <t>car</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
           <t>ball</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>chair</t>
-        </is>
-      </c>
       <c r="M25" t="inlineStr">
         <is>
           <t>right</t>
@@ -2886,19 +2886,19 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P25" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="Q25" t="n">
         <v>0.53</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>0.4</v>
       </c>
       <c r="R25" t="inlineStr">
         <is>
@@ -2915,10 +2915,10 @@
         <v>6</v>
       </c>
       <c r="V25" t="n">
+        <v>11</v>
+      </c>
+      <c r="W25" t="n">
         <v>1</v>
-      </c>
-      <c r="W25" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="26">
@@ -2950,12 +2950,12 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_14.jpg</t>
+          <t>stimuli/ball/ball_11.jpg</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_11.jpg</t>
+          <t>stimuli/chair/chair_49.jpg</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2970,12 +2970,12 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2985,19 +2985,19 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0.73</v>
+        <v>0.6</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.6</v>
+        <v>0.47</v>
       </c>
       <c r="R26" t="inlineStr">
         <is>
@@ -3014,10 +3014,10 @@
         <v>14</v>
       </c>
       <c r="V26" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="W26" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27">
@@ -3049,12 +3049,12 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_49.jpg</t>
+          <t>stimuli/pencil/pencil_14.jpg</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>stimuli/car/car_34.jpg</t>
+          <t>stimuli/hand/hand_34.jpg</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3069,38 +3069,38 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0.53</v>
+        <v>0.8</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.26</v>
+        <v>0.4</v>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S27" t="n">
@@ -3113,10 +3113,10 @@
         <v>13</v>
       </c>
       <c r="V27" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="W27" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28">
@@ -3148,12 +3148,12 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>stimuli/house/house_06.jpg</t>
+          <t>stimuli/bread/bread_07.jpg</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_07.jpg</t>
+          <t>stimuli/lamp/lamp_22.jpg</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -3183,19 +3183,19 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0.75</v>
+        <v>0.31</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.31</v>
+        <v>0.2</v>
       </c>
       <c r="R28" t="inlineStr">
         <is>
@@ -3212,10 +3212,10 @@
         <v>13</v>
       </c>
       <c r="V28" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="W28" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="29">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_19.jpg</t>
+          <t>stimuli/house/house_06.jpg</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_22.jpg</t>
+          <t>stimuli/phone/phone_23.jpg</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>lamp</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -3291,10 +3291,10 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0.42</v>
+        <v>0.8</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="R29" t="inlineStr">
         <is>
@@ -3311,10 +3311,10 @@
         <v>5</v>
       </c>
       <c r="V29" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W29" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="30">
@@ -3346,12 +3346,12 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_06.jpg</t>
+          <t>stimuli/bicycle/bicycle_17.jpg</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_18.jpg</t>
+          <t>stimuli/lamp/lamp_22.jpg</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3366,12 +3366,12 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -3390,10 +3390,10 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.53</v>
+        <v>0.31</v>
       </c>
       <c r="R30" t="inlineStr">
         <is>
@@ -3410,10 +3410,10 @@
         <v>9</v>
       </c>
       <c r="V30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W30" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="31">
@@ -3445,7 +3445,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_17.jpg</t>
+          <t>stimuli/ball/ball_06.jpg</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3465,7 +3465,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -3489,7 +3489,7 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.75</v>
       </c>
       <c r="Q31" t="n">
         <v>0.27</v>
@@ -3509,7 +3509,7 @@
         <v>6</v>
       </c>
       <c r="V31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W31" t="n">
         <v>12</v>
@@ -3544,7 +3544,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_06.jpg</t>
+          <t>stimuli/hand/hand_19.jpg</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -3588,7 +3588,7 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0.8</v>
+        <v>0.58</v>
       </c>
       <c r="Q32" t="n">
         <v>0.47</v>
@@ -3608,7 +3608,7 @@
         <v>4</v>
       </c>
       <c r="V32" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="W32" t="n">
         <v>17</v>
@@ -3643,12 +3643,12 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_44.jpg</t>
+          <t>stimuli/jacket/jacket_18.jpg</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_07.jpg</t>
+          <t>stimuli/lamp/lamp_22.jpg</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -3663,17 +3663,17 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -3683,18 +3683,18 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.58</v>
+        <v>0.47</v>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S33" t="n">
@@ -3707,10 +3707,10 @@
         <v>1</v>
       </c>
       <c r="V33" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W33" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="34">
@@ -3742,7 +3742,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_42.jpg</t>
+          <t>stimuli/lamp/lamp_22.jpg</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3762,7 +3762,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -3772,28 +3772,28 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0.33</v>
+        <v>0.53</v>
       </c>
       <c r="Q34" t="n">
         <v>0.2</v>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S34" t="n">
@@ -3806,7 +3806,7 @@
         <v>2</v>
       </c>
       <c r="V34" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="W34" t="n">
         <v>6</v>
@@ -3841,7 +3841,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_07.jpg</t>
+          <t>stimuli/guitar/guitar_07.jpg</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3861,7 +3861,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>guitar</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -3876,16 +3876,16 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.47</v>
       </c>
       <c r="Q35" t="n">
         <v>0.2</v>
@@ -3905,7 +3905,7 @@
         <v>7</v>
       </c>
       <c r="V35" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="W35" t="n">
         <v>4</v>
@@ -3940,12 +3940,12 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>stimuli/phone/phone_23.jpg</t>
+          <t>stimuli/dog/dog_42.jpg</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_07.jpg</t>
+          <t>stimuli/ball/ball_06.jpg</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3960,38 +3960,38 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P36" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.47</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.53</v>
+        <v>0.2</v>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S36" t="n">
@@ -4004,10 +4004,10 @@
         <v>10</v>
       </c>
       <c r="V36" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="W36" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -4039,12 +4039,12 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_07.jpg</t>
+          <t>stimuli/bread/bread_07.jpg</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_06.jpg</t>
+          <t>stimuli/lamp/lamp_22.jpg</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -4059,12 +4059,12 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -4083,10 +4083,10 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.27</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="R37" t="inlineStr">
         <is>
@@ -4103,10 +4103,10 @@
         <v>8</v>
       </c>
       <c r="V37" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="W37" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="38">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>stimuli/house/house_06.jpg</t>
+          <t>stimuli/dog/dog_42.jpg</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_06.jpg</t>
+          <t>stimuli/flower/flower_49.jpg</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4257,12 +4257,12 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -4281,10 +4281,10 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.4</v>
+        <v>0.53</v>
       </c>
       <c r="R39" t="inlineStr">
         <is>
@@ -4301,10 +4301,10 @@
         <v>17</v>
       </c>
       <c r="V39" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="W39" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="40">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_17.jpg</t>
+          <t>stimuli/guitar/guitar_07.jpg</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -4356,7 +4356,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>guitar</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -4380,7 +4380,7 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="Q40" t="n">
         <v>0.26</v>
@@ -4400,7 +4400,7 @@
         <v>14</v>
       </c>
       <c r="V40" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="W40" t="n">
         <v>12</v>
@@ -4435,12 +4435,12 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_12.jpg</t>
+          <t>stimuli/ball/ball_11.jpg</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_36.jpg</t>
+          <t>stimuli/lamp/lamp_13.jpg</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4455,17 +4455,17 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -4475,18 +4475,18 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.31</v>
+        <v>0.25</v>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S41" t="n">
@@ -4499,10 +4499,10 @@
         <v>16</v>
       </c>
       <c r="V41" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="W41" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="42">
@@ -4534,7 +4534,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_36.jpg</t>
+          <t>stimuli/dog/dog_19.jpg</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -4554,7 +4554,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -4569,16 +4569,16 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0.36</v>
+        <v>0.47</v>
       </c>
       <c r="Q42" t="n">
         <v>0.25</v>
@@ -4598,7 +4598,7 @@
         <v>10</v>
       </c>
       <c r="V42" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W42" t="n">
         <v>13</v>
@@ -4633,12 +4633,12 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_13.jpg</t>
+          <t>stimuli/bicycle/bicycle_22.jpg</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_36.jpg</t>
+          <t>stimuli/lamp/lamp_13.jpg</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -4653,12 +4653,12 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -4668,19 +4668,19 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P43" t="n">
-        <v>0.58</v>
+        <v>0.47</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.42</v>
+        <v>0.36</v>
       </c>
       <c r="R43" t="inlineStr">
         <is>
@@ -4697,10 +4697,10 @@
         <v>1</v>
       </c>
       <c r="V43" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="W43" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="44">
@@ -4737,7 +4737,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_13.jpg</t>
+          <t>stimuli/flower/flower_36.jpg</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -4757,7 +4757,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>lamp</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -4779,7 +4779,7 @@
         <v>0.8</v>
       </c>
       <c r="Q44" t="n">
-        <v>0.42</v>
+        <v>0.47</v>
       </c>
       <c r="R44" t="inlineStr">
         <is>
@@ -4799,7 +4799,7 @@
         <v>4</v>
       </c>
       <c r="W44" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="45">
@@ -4866,12 +4866,12 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P45" t="n">
@@ -4930,7 +4930,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_19.jpg</t>
+          <t>stimuli/hammer/hammer_13.jpg</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -4950,7 +4950,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -4960,12 +4960,12 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
@@ -4974,14 +4974,14 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.75</v>
       </c>
       <c r="Q46" t="n">
         <v>0.47</v>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S46" t="n">
@@ -4994,7 +4994,7 @@
         <v>9</v>
       </c>
       <c r="V46" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W46" t="n">
         <v>13</v>
@@ -5029,12 +5029,12 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_22.jpg</t>
+          <t>stimuli/jacket/jacket_12.jpg</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_13.jpg</t>
+          <t>stimuli/bread/bread_34.jpg</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -5049,38 +5049,38 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>lamp</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.33</v>
       </c>
       <c r="Q47" t="n">
-        <v>0.58</v>
+        <v>0.2</v>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S47" t="n">
@@ -5093,10 +5093,10 @@
         <v>8</v>
       </c>
       <c r="V47" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="W47" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
     </row>
     <row r="48">
@@ -5128,12 +5128,12 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_19.jpg</t>
+          <t>stimuli/lamp/lamp_13.jpg</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_11.jpg</t>
+          <t>stimuli/pencil/pencil_14.jpg</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -5148,12 +5148,12 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -5163,19 +5163,19 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P48" t="n">
-        <v>0.8</v>
+        <v>0.64</v>
       </c>
       <c r="Q48" t="n">
-        <v>0.33</v>
+        <v>0.47</v>
       </c>
       <c r="R48" t="inlineStr">
         <is>
@@ -5192,10 +5192,10 @@
         <v>7</v>
       </c>
       <c r="V48" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="W48" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
     </row>
     <row r="49">
@@ -5227,7 +5227,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_34.jpg</t>
+          <t>stimuli/ball/ball_11.jpg</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -5247,7 +5247,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -5257,12 +5257,12 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
@@ -5271,14 +5271,14 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="Q49" t="n">
         <v>0.2</v>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S49" t="n">
@@ -5291,7 +5291,7 @@
         <v>5</v>
       </c>
       <c r="V49" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W49" t="n">
         <v>9</v>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_13.jpg</t>
+          <t>stimuli/car/car_34.jpg</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -5346,7 +5346,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>lamp</t>
+          <t>car</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -5361,16 +5361,16 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P50" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="Q50" t="n">
         <v>0.2</v>
@@ -5390,7 +5390,7 @@
         <v>2</v>
       </c>
       <c r="V50" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="W50" t="n">
         <v>8</v>
@@ -5425,7 +5425,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_14.jpg</t>
+          <t>stimuli/guitar/guitar_12.jpg</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -5445,7 +5445,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>guitar</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -5455,28 +5455,28 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P51" t="n">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="Q51" t="n">
         <v>0.33</v>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S51" t="n">
@@ -5489,7 +5489,7 @@
         <v>6</v>
       </c>
       <c r="V51" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="W51" t="n">
         <v>9</v>
@@ -5529,7 +5529,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_34.jpg</t>
+          <t>stimuli/bread/bread_34.jpg</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -5549,33 +5549,33 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P52" t="n">
         <v>0.8</v>
       </c>
       <c r="Q52" t="n">
-        <v>0.33</v>
+        <v>0.53</v>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S52" t="n">
@@ -5591,7 +5591,7 @@
         <v>11</v>
       </c>
       <c r="W52" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="53">
@@ -5623,12 +5623,12 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_14.jpg</t>
+          <t>stimuli/ball/ball_11.jpg</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>stimuli/house/house_48.jpg</t>
+          <t>stimuli/car/car_34.jpg</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -5643,12 +5643,12 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>car</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -5658,19 +5658,19 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P53" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="Q53" t="n">
-        <v>0.47</v>
+        <v>0.26</v>
       </c>
       <c r="R53" t="inlineStr">
         <is>
@@ -5687,10 +5687,10 @@
         <v>13</v>
       </c>
       <c r="V53" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="W53" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="54">
@@ -5722,7 +5722,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>stimuli/house/house_06.jpg</t>
+          <t>stimuli/dog/dog_42.jpg</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -5742,7 +5742,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -5752,28 +5752,28 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P54" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="Q54" t="n">
         <v>0.25</v>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S54" t="n">
@@ -5786,7 +5786,7 @@
         <v>13</v>
       </c>
       <c r="V54" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="W54" t="n">
         <v>17</v>
@@ -5821,12 +5821,12 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_06.jpg</t>
+          <t>stimuli/bread/bread_07.jpg</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_19.jpg</t>
+          <t>stimuli/lamp/lamp_22.jpg</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -5856,19 +5856,19 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P55" t="n">
-        <v>0.64</v>
+        <v>0.36</v>
       </c>
       <c r="Q55" t="n">
-        <v>0.42</v>
+        <v>0.25</v>
       </c>
       <c r="R55" t="inlineStr">
         <is>
@@ -5885,10 +5885,10 @@
         <v>5</v>
       </c>
       <c r="V55" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W55" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="56">
@@ -5920,7 +5920,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_44.jpg</t>
+          <t>stimuli/jacket/jacket_18.jpg</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -5940,7 +5940,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -5950,28 +5950,28 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P56" t="n">
-        <v>0.58</v>
+        <v>0.53</v>
       </c>
       <c r="Q56" t="n">
         <v>0.36</v>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S56" t="n">
@@ -5984,7 +5984,7 @@
         <v>9</v>
       </c>
       <c r="V56" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W56" t="n">
         <v>17</v>
@@ -6019,7 +6019,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_19.jpg</t>
+          <t>stimuli/chair/chair_06.jpg</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -6039,7 +6039,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -6054,16 +6054,16 @@
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P57" t="n">
-        <v>0.53</v>
+        <v>0.8</v>
       </c>
       <c r="Q57" t="n">
         <v>0.36</v>
@@ -6083,7 +6083,7 @@
         <v>6</v>
       </c>
       <c r="V57" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="W57" t="n">
         <v>14</v>
@@ -6118,12 +6118,12 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_18.jpg</t>
+          <t>stimuli/hammer/hammer_44.jpg</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_07.jpg</t>
+          <t>stimuli/hand/hand_19.jpg</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -6138,38 +6138,38 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P58" t="n">
-        <v>0.64</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q58" t="n">
-        <v>0.53</v>
+        <v>0.58</v>
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S58" t="n">
@@ -6182,10 +6182,10 @@
         <v>4</v>
       </c>
       <c r="V58" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W58" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="59">
@@ -6247,12 +6247,12 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
@@ -6268,7 +6268,7 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S59" t="n">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>stimuli/phone/phone_23.jpg</t>
+          <t>stimuli/guitar/guitar_07.jpg</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -6336,7 +6336,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>guitar</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -6346,12 +6346,12 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
@@ -6360,14 +6360,14 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>0.58</v>
+        <v>0.4</v>
       </c>
       <c r="Q60" t="n">
         <v>0.2</v>
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S60" t="n">
@@ -6380,7 +6380,7 @@
         <v>2</v>
       </c>
       <c r="V60" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="W60" t="n">
         <v>6</v>
@@ -6415,12 +6415,12 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>stimuli/fish/fish_37.jpg</t>
+          <t>stimuli/house/house_06.jpg</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>stimuli/house/house_06.jpg</t>
+          <t>stimuli/chair/chair_06.jpg</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -6435,22 +6435,22 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>fish</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
@@ -6459,14 +6459,14 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>0.53</v>
+        <v>0.33</v>
       </c>
       <c r="Q61" t="n">
-        <v>0.33</v>
+        <v>0.2</v>
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S61" t="n">
@@ -6479,10 +6479,10 @@
         <v>7</v>
       </c>
       <c r="V61" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="W61" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="62">
@@ -6514,12 +6514,12 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_19.jpg</t>
+          <t>stimuli/guitar/guitar_07.jpg</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_06.jpg</t>
+          <t>stimuli/ball/ball_06.jpg</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -6534,38 +6534,38 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>guitar</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P62" t="n">
-        <v>0.8</v>
+        <v>0.53</v>
       </c>
       <c r="Q62" t="n">
-        <v>0.27</v>
+        <v>0.2</v>
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S62" t="n">
@@ -6578,10 +6578,10 @@
         <v>10</v>
       </c>
       <c r="V62" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="W62" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -6613,12 +6613,12 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_07.jpg</t>
+          <t>stimuli/fish/fish_37.jpg</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>stimuli/house/house_06.jpg</t>
+          <t>stimuli/chair/chair_06.jpg</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -6633,12 +6633,12 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>fish</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -6648,19 +6648,19 @@
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P63" t="n">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="Q63" t="n">
-        <v>0.47</v>
+        <v>0.33</v>
       </c>
       <c r="R63" t="inlineStr">
         <is>
@@ -6677,10 +6677,10 @@
         <v>8</v>
       </c>
       <c r="V63" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="W63" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="64">
@@ -6742,12 +6742,12 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
@@ -6763,7 +6763,7 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S64" t="n">
@@ -6811,12 +6811,12 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_07.jpg</t>
+          <t>stimuli/fish/fish_37.jpg</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_44.jpg</t>
+          <t>stimuli/house/house_06.jpg</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -6831,22 +6831,22 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>fish</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>house</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
@@ -6855,14 +6855,14 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>0.73</v>
+        <v>0.8</v>
       </c>
       <c r="Q65" t="n">
-        <v>0.27</v>
+        <v>0.6</v>
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S65" t="n">
@@ -6875,10 +6875,10 @@
         <v>17</v>
       </c>
       <c r="V65" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="W65" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="66">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>stimuli/house/house_06.jpg</t>
+          <t>stimuli/dog/dog_42.jpg</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_18.jpg</t>
+          <t>stimuli/flower/flower_49.jpg</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -6954,10 +6954,10 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>0.67</v>
+        <v>0.73</v>
       </c>
       <c r="Q66" t="n">
-        <v>0.27</v>
+        <v>0.6</v>
       </c>
       <c r="R66" t="inlineStr">
         <is>
@@ -6974,10 +6974,10 @@
         <v>14</v>
       </c>
       <c r="V66" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="W66" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="67">
@@ -7009,7 +7009,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_13.jpg</t>
+          <t>stimuli/hand/hand_34.jpg</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -7029,7 +7029,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -7039,7 +7039,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -7049,18 +7049,18 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P67" t="n">
-        <v>0.47</v>
+        <v>0.53</v>
       </c>
       <c r="Q67" t="n">
         <v>0.2</v>
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S67" t="n">
@@ -7073,7 +7073,7 @@
         <v>16</v>
       </c>
       <c r="V67" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W67" t="n">
         <v>13</v>
@@ -7108,12 +7108,12 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_19.jpg</t>
+          <t>stimuli/chair/chair_49.jpg</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_36.jpg</t>
+          <t>stimuli/lamp/lamp_13.jpg</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -7128,12 +7128,12 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
@@ -7152,10 +7152,10 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>0.47</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q68" t="n">
-        <v>0.36</v>
+        <v>0.31</v>
       </c>
       <c r="R68" t="inlineStr">
         <is>
@@ -7172,10 +7172,10 @@
         <v>10</v>
       </c>
       <c r="V68" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="W68" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="69">
@@ -7212,7 +7212,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_13.jpg</t>
+          <t>stimuli/flower/flower_36.jpg</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -7232,33 +7232,33 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>lamp</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P69" t="n">
         <v>0.64</v>
       </c>
       <c r="Q69" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S69" t="n">
@@ -7274,7 +7274,7 @@
         <v>8</v>
       </c>
       <c r="W69" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="70">
@@ -7336,17 +7336,17 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P70" t="n">
@@ -7357,7 +7357,7 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S70" t="n">
@@ -7405,7 +7405,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_22.jpg</t>
+          <t>stimuli/dog/dog_19.jpg</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -7425,7 +7425,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -7435,28 +7435,28 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P71" t="n">
-        <v>0.58</v>
+        <v>0.64</v>
       </c>
       <c r="Q71" t="n">
         <v>0.47</v>
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S71" t="n">
@@ -7469,7 +7469,7 @@
         <v>4</v>
       </c>
       <c r="V71" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="W71" t="n">
         <v>14</v>
@@ -7539,12 +7539,12 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P72" t="n">
@@ -7603,12 +7603,12 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_14.jpg</t>
+          <t>stimuli/hammer/hammer_13.jpg</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_34.jpg</t>
+          <t>stimuli/lamp/lamp_13.jpg</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -7623,17 +7623,17 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -7643,18 +7643,18 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P73" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="Q73" t="n">
-        <v>0.2</v>
+        <v>0.58</v>
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S73" t="n">
@@ -7667,10 +7667,10 @@
         <v>8</v>
       </c>
       <c r="V73" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="W73" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="74">
@@ -7702,12 +7702,12 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_12.jpg</t>
+          <t>stimuli/jacket/jacket_12.jpg</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_49.jpg</t>
+          <t>stimuli/bread/bread_34.jpg</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -7722,12 +7722,12 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -7737,19 +7737,19 @@
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P74" t="n">
-        <v>0.58</v>
+        <v>0.4</v>
       </c>
       <c r="Q74" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="R74" t="inlineStr">
         <is>
@@ -7766,10 +7766,10 @@
         <v>7</v>
       </c>
       <c r="V74" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="W74" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="75">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_13.jpg</t>
+          <t>stimuli/bicycle/bicycle_22.jpg</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_11.jpg</t>
+          <t>stimuli/guitar/guitar_12.jpg</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -7821,17 +7821,17 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>lamp</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>guitar</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -7841,18 +7841,18 @@
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P75" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="Q75" t="n">
-        <v>0.4</v>
+        <v>0.64</v>
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S75" t="n">
@@ -7865,10 +7865,10 @@
         <v>5</v>
       </c>
       <c r="V75" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="W75" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
     </row>
     <row r="76">
@@ -7900,12 +7900,12 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_36.jpg</t>
+          <t>stimuli/pencil/pencil_14.jpg</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_12.jpg</t>
+          <t>stimuli/bread/bread_34.jpg</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -7944,10 +7944,10 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="Q76" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.4</v>
       </c>
       <c r="R76" t="inlineStr">
         <is>
@@ -7964,10 +7964,10 @@
         <v>2</v>
       </c>
       <c r="V76" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="W76" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="77">
@@ -7999,12 +7999,12 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_12.jpg</t>
+          <t>stimuli/ball/ball_11.jpg</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>stimuli/house/house_48.jpg</t>
+          <t>stimuli/hand/hand_34.jpg</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -8019,12 +8019,12 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -8043,10 +8043,10 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>0.75</v>
+        <v>0.53</v>
       </c>
       <c r="Q77" t="n">
-        <v>0.33</v>
+        <v>0.27</v>
       </c>
       <c r="R77" t="inlineStr">
         <is>
@@ -8063,10 +8063,10 @@
         <v>6</v>
       </c>
       <c r="V77" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="W77" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="78">
@@ -8103,7 +8103,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_34.jpg</t>
+          <t>stimuli/jacket/jacket_12.jpg</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -8123,12 +8123,12 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -8138,18 +8138,18 @@
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P78" t="n">
         <v>0.8</v>
       </c>
       <c r="Q78" t="n">
-        <v>0.53</v>
+        <v>0.67</v>
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S78" t="n">
@@ -8165,7 +8165,7 @@
         <v>11</v>
       </c>
       <c r="W78" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="79">
@@ -8197,12 +8197,12 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_14.jpg</t>
+          <t>stimuli/hand/hand_34.jpg</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_34.jpg</t>
+          <t>stimuli/car/car_34.jpg</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -8217,38 +8217,38 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>car</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P79" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="Q79" t="n">
-        <v>0.4</v>
+        <v>0.26</v>
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S79" t="n">
@@ -8261,10 +8261,10 @@
         <v>13</v>
       </c>
       <c r="V79" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="W79" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="80">
@@ -8296,7 +8296,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_18.jpg</t>
+          <t>stimuli/ball/ball_06.jpg</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -8316,7 +8316,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -8326,12 +8326,12 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
@@ -8340,14 +8340,14 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>0.42</v>
+        <v>0.58</v>
       </c>
       <c r="Q80" t="n">
         <v>0.2</v>
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S80" t="n">
@@ -8360,7 +8360,7 @@
         <v>13</v>
       </c>
       <c r="V80" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="W80" t="n">
         <v>14</v>
@@ -8395,12 +8395,12 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_06.jpg</t>
+          <t>stimuli/flower/flower_49.jpg</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_19.jpg</t>
+          <t>stimuli/phone/phone_23.jpg</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -8415,38 +8415,38 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P81" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.75</v>
       </c>
       <c r="Q81" t="n">
-        <v>0.42</v>
+        <v>0.31</v>
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S81" t="n">
@@ -8459,10 +8459,10 @@
         <v>5</v>
       </c>
       <c r="V81" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="W81" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
     </row>
     <row r="82">
@@ -8494,12 +8494,12 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_49.jpg</t>
+          <t>stimuli/hammer/hammer_44.jpg</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>stimuli/phone/phone_23.jpg</t>
+          <t>stimuli/lamp/lamp_22.jpg</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -8514,38 +8514,38 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P82" t="n">
-        <v>0.8</v>
+        <v>0.58</v>
       </c>
       <c r="Q82" t="n">
-        <v>0.36</v>
+        <v>0.31</v>
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S82" t="n">
@@ -8558,10 +8558,10 @@
         <v>9</v>
       </c>
       <c r="V82" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W82" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="83">
@@ -8593,12 +8593,12 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_17.jpg</t>
+          <t>stimuli/hand/hand_19.jpg</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_22.jpg</t>
+          <t>stimuli/phone/phone_23.jpg</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -8613,12 +8613,12 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>lamp</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
@@ -8637,10 +8637,10 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.53</v>
       </c>
       <c r="Q83" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="R83" t="inlineStr">
         <is>
@@ -8657,10 +8657,10 @@
         <v>6</v>
       </c>
       <c r="V83" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="W83" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="84">
@@ -8697,7 +8697,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>stimuli/fish/fish_37.jpg</t>
+          <t>stimuli/bread/bread_07.jpg</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -8717,17 +8717,17 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>fish</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O84" t="inlineStr">
@@ -8739,11 +8739,11 @@
         <v>0.64</v>
       </c>
       <c r="Q84" t="n">
-        <v>0.33</v>
+        <v>0.53</v>
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S84" t="n">
@@ -8759,7 +8759,7 @@
         <v>10</v>
       </c>
       <c r="W84" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="85">
@@ -8791,12 +8791,12 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_44.jpg</t>
+          <t>stimuli/bicycle/bicycle_17.jpg</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>stimuli/phone/phone_23.jpg</t>
+          <t>stimuli/lamp/lamp_22.jpg</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -8811,38 +8811,38 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P85" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="Q85" t="n">
-        <v>0.53</v>
+        <v>0.47</v>
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S85" t="n">
@@ -8855,10 +8855,10 @@
         <v>1</v>
       </c>
       <c r="V85" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="W85" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="86">
@@ -8890,12 +8890,12 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_07.jpg</t>
+          <t>stimuli/bread/bread_07.jpg</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_49.jpg</t>
+          <t>stimuli/fish/fish_37.jpg</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -8910,17 +8910,17 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>fish</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
@@ -8930,18 +8930,18 @@
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P86" t="n">
-        <v>0.4</v>
+        <v>0.64</v>
       </c>
       <c r="Q86" t="n">
-        <v>0.2</v>
+        <v>0.47</v>
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S86" t="n">
@@ -8954,10 +8954,10 @@
         <v>2</v>
       </c>
       <c r="V86" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="W86" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="87">
@@ -8989,12 +8989,12 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_07.jpg</t>
+          <t>stimuli/house/house_06.jpg</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_22.jpg</t>
+          <t>stimuli/chair/chair_06.jpg</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -9009,38 +9009,38 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>lamp</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P87" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.33</v>
       </c>
       <c r="Q87" t="n">
-        <v>0.58</v>
+        <v>0.2</v>
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S87" t="n">
@@ -9053,10 +9053,10 @@
         <v>7</v>
       </c>
       <c r="V87" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="W87" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
     </row>
     <row r="88">
@@ -9093,7 +9093,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_06.jpg</t>
+          <t>stimuli/dog/dog_42.jpg</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -9113,7 +9113,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
@@ -9123,19 +9123,19 @@
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P88" t="n">
         <v>0.6</v>
       </c>
       <c r="Q88" t="n">
-        <v>0.2</v>
+        <v>0.47</v>
       </c>
       <c r="R88" t="inlineStr">
         <is>
@@ -9155,7 +9155,7 @@
         <v>12</v>
       </c>
       <c r="W88" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="89">
@@ -9187,12 +9187,12 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_42.jpg</t>
+          <t>stimuli/guitar/guitar_07.jpg</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_17.jpg</t>
+          <t>stimuli/ball/ball_06.jpg</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -9207,22 +9207,22 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>guitar</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O89" t="inlineStr">
@@ -9231,14 +9231,14 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>0.53</v>
+        <v>0.6</v>
       </c>
       <c r="Q89" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S89" t="n">
@@ -9251,10 +9251,10 @@
         <v>8</v>
       </c>
       <c r="V89" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="W89" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90">
@@ -9291,7 +9291,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>stimuli/house/house_06.jpg</t>
+          <t>stimuli/bicycle/bicycle_17.jpg</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -9311,33 +9311,33 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P90" t="n">
         <v>0.73</v>
       </c>
       <c r="Q90" t="n">
-        <v>0.53</v>
+        <v>0.27</v>
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S90" t="n">
@@ -9353,7 +9353,7 @@
         <v>12</v>
       </c>
       <c r="W90" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="91">
@@ -9390,7 +9390,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_06.jpg</t>
+          <t>stimuli/hammer/hammer_44.jpg</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -9410,17 +9410,17 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O91" t="inlineStr">
@@ -9432,11 +9432,11 @@
         <v>0.67</v>
       </c>
       <c r="Q91" t="n">
-        <v>0.4</v>
+        <v>0.27</v>
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S91" t="n">
@@ -9452,7 +9452,7 @@
         <v>5</v>
       </c>
       <c r="W91" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="92">
@@ -9489,7 +9489,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>stimuli/house/house_06.jpg</t>
+          <t>stimuli/hand/hand_19.jpg</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -9509,7 +9509,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -9519,19 +9519,19 @@
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P92" t="n">
         <v>0.8</v>
       </c>
       <c r="Q92" t="n">
-        <v>0.67</v>
+        <v>0.2</v>
       </c>
       <c r="R92" t="inlineStr">
         <is>
@@ -9551,7 +9551,7 @@
         <v>13</v>
       </c>
       <c r="W92" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="93">
@@ -9583,12 +9583,12 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_12.jpg</t>
+          <t>stimuli/ball/ball_11.jpg</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_13.jpg</t>
+          <t>stimuli/guitar/guitar_12.jpg</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -9603,38 +9603,38 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>lamp</t>
+          <t>guitar</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P93" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="Q93" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S93" t="n">
@@ -9647,10 +9647,10 @@
         <v>16</v>
       </c>
       <c r="V93" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="W93" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="94">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_11.jpg</t>
+          <t>stimuli/hammer/hammer_13.jpg</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_12.jpg</t>
+          <t>stimuli/lamp/lamp_13.jpg</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -9702,38 +9702,38 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P94" t="n">
-        <v>0.8</v>
+        <v>0.53</v>
       </c>
       <c r="Q94" t="n">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S94" t="n">
@@ -9746,10 +9746,10 @@
         <v>10</v>
       </c>
       <c r="V94" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="W94" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="95">
@@ -9781,14 +9781,14 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
+          <t>stimuli/bicycle/bicycle_22.jpg</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
           <t>stimuli/guitar/guitar_12.jpg</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>stimuli/car/car_34.jpg</t>
-        </is>
-      </c>
       <c r="I95" t="inlineStr">
         <is>
           <t>jacket</t>
@@ -9801,38 +9801,38 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
           <t>guitar</t>
         </is>
       </c>
-      <c r="L95" t="inlineStr">
-        <is>
-          <t>car</t>
-        </is>
-      </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P95" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="Q95" t="n">
         <v>0.31</v>
       </c>
-      <c r="Q95" t="n">
-        <v>0.2</v>
-      </c>
       <c r="R95" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S95" t="n">
@@ -9845,10 +9845,10 @@
         <v>1</v>
       </c>
       <c r="V95" t="n">
+        <v>2</v>
+      </c>
+      <c r="W95" t="n">
         <v>13</v>
-      </c>
-      <c r="W95" t="n">
-        <v>11</v>
       </c>
     </row>
     <row r="96">
@@ -9880,12 +9880,12 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>stimuli/house/house_48.jpg</t>
+          <t>stimuli/hand/hand_34.jpg</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_36.jpg</t>
+          <t>stimuli/lamp/lamp_13.jpg</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -9900,12 +9900,12 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
@@ -9915,19 +9915,19 @@
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P96" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q96" t="n">
-        <v>0.47</v>
+        <v>0.42</v>
       </c>
       <c r="R96" t="inlineStr">
         <is>
@@ -9944,10 +9944,10 @@
         <v>3</v>
       </c>
       <c r="V96" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W96" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="97">
@@ -9979,12 +9979,12 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_19.jpg</t>
+          <t>stimuli/hammer/hammer_13.jpg</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_13.jpg</t>
+          <t>stimuli/pencil/pencil_14.jpg</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -9999,38 +9999,38 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>lamp</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P97" t="n">
-        <v>0.64</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q97" t="n">
-        <v>0.47</v>
+        <v>0.27</v>
       </c>
       <c r="R97" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S97" t="n">
@@ -10043,10 +10043,10 @@
         <v>4</v>
       </c>
       <c r="V97" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W97" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="98">
@@ -10078,12 +10078,12 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_34.jpg</t>
+          <t>stimuli/flower/flower_36.jpg</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_36.jpg</t>
+          <t>stimuli/guitar/guitar_12.jpg</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>guitar</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -10113,19 +10113,19 @@
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P98" t="n">
-        <v>0.8</v>
+        <v>0.58</v>
       </c>
       <c r="Q98" t="n">
-        <v>0.58</v>
+        <v>0.47</v>
       </c>
       <c r="R98" t="inlineStr">
         <is>
@@ -10142,10 +10142,10 @@
         <v>9</v>
       </c>
       <c r="V98" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="W98" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="99">
@@ -10177,12 +10177,12 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_12.jpg</t>
+          <t>stimuli/dog/dog_19.jpg</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_34.jpg</t>
+          <t>stimuli/lamp/lamp_13.jpg</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -10197,12 +10197,12 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
@@ -10212,19 +10212,19 @@
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P99" t="n">
-        <v>0.33</v>
+        <v>0.75</v>
       </c>
       <c r="Q99" t="n">
-        <v>0.2</v>
+        <v>0.58</v>
       </c>
       <c r="R99" t="inlineStr">
         <is>
@@ -10241,10 +10241,10 @@
         <v>8</v>
       </c>
       <c r="V99" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="W99" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="100">
@@ -10276,12 +10276,12 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_22.jpg</t>
+          <t>stimuli/jacket/jacket_12.jpg</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>stimuli/lamp/lamp_13.jpg</t>
+          <t>stimuli/bread/bread_34.jpg</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -10296,38 +10296,38 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>lamp</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="P100" t="n">
-        <v>0.75</v>
+        <v>0.4</v>
       </c>
       <c r="Q100" t="n">
-        <v>0.64</v>
+        <v>0.27</v>
       </c>
       <c r="R100" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S100" t="n">
@@ -10340,10 +10340,10 @@
         <v>7</v>
       </c>
       <c r="V100" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="W100" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
     </row>
     <row r="101">
@@ -10375,12 +10375,12 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>stimuli/guitar/guitar_12.jpg</t>
+          <t>stimuli/lamp/lamp_13.jpg</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_49.jpg</t>
+          <t>stimuli/house/house_48.jpg</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -10395,22 +10395,22 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>guitar</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>house</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O101" t="inlineStr">
@@ -10419,14 +10419,14 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>0.64</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q101" t="n">
-        <v>0.27</v>
+        <v>0.2</v>
       </c>
       <c r="R101" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="S101" t="n">
@@ -10439,10 +10439,10 @@
         <v>5</v>
       </c>
       <c r="V101" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="W101" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="102">
@@ -10474,7 +10474,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>stimuli/pencil/pencil_14.jpg</t>
+          <t>stimuli/car/car_34.jpg</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -10494,7 +10494,7 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>pencil</t>
+          <t>car</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -10504,28 +10504,28 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P102" t="n">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="Q102" t="n">
         <v>0.4</v>
       </c>
       <c r="R102" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S102" t="n">
@@ -10538,7 +10538,7 @@
         <v>2</v>
       </c>
       <c r="V102" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="W102" t="n">
         <v>3</v>
@@ -10573,12 +10573,12 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>stimuli/car/car_34.jpg</t>
+          <t>stimuli/ball/ball_11.jpg</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_13.jpg</t>
+          <t>stimuli/chair/chair_49.jpg</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -10593,38 +10593,38 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="P103" t="n">
-        <v>0.73</v>
+        <v>0.53</v>
       </c>
       <c r="Q103" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="R103" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="S103" t="n">
@@ -10637,10 +10637,10 @@
         <v>6</v>
       </c>
       <c r="V103" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="W103" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="104">
@@ -10672,7 +10672,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_11.jpg</t>
+          <t>stimuli/pencil/pencil_14.jpg</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -10692,7 +10692,7 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>pencil</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -10702,28 +10702,28 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="P104" t="n">
-        <v>0.6</v>
+        <v>0.73</v>
       </c>
       <c r="Q104" t="n">
         <v>0.33</v>
       </c>
       <c r="R104" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>center</t>
         </is>
       </c>
       <c r="S104" t="n">
@@ -10736,7 +10736,7 @@
         <v>14</v>
       </c>
       <c r="V104" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="W104" t="n">
         <v>8</v>

--- a/psychopy_exp_files/sequences/learning_block3_fixed-middle-10_24.xlsx
+++ b/psychopy_exp_files/sequences/learning_block3_fixed-middle-10_24.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_44.jpg</t>
+          <t>stimuli/hand/hand_19.jpg</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -594,7 +594,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -638,7 +638,7 @@
         <v>13</v>
       </c>
       <c r="V2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W2" t="n">
         <v>14</v>
@@ -673,7 +673,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_19.jpg</t>
+          <t>stimuli/jacket/jacket_18.jpg</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -737,7 +737,7 @@
         <v>5</v>
       </c>
       <c r="V3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W3" t="n">
         <v>17</v>
@@ -772,12 +772,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_18.jpg</t>
+          <t>stimuli/chair/chair_06.jpg</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_07.jpg</t>
+          <t>stimuli/flower/flower_49.jpg</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -792,12 +792,12 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -836,10 +836,10 @@
         <v>9</v>
       </c>
       <c r="V4" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="W4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
@@ -866,12 +866,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_49.jpg</t>
+          <t>stimuli/bicycle/bicycle_17.jpg</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_06.jpg</t>
+          <t>stimuli/bread/bread_07.jpg</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -886,12 +886,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -932,10 +932,10 @@
         <v>9</v>
       </c>
       <c r="U5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="V5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W5" t="n">
         <v>17</v>
@@ -960,17 +960,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_49.jpg</t>
+          <t>stimuli/bicycle/bicycle_17.jpg</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_06.jpg</t>
+          <t>stimuli/bread/bread_07.jpg</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_17.jpg</t>
+          <t>stimuli/hammer/hammer_44.jpg</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -980,17 +980,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1028,13 +1028,13 @@
         <v>6</v>
       </c>
       <c r="T6" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="U6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V6" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="W6" t="n">
         <v>14</v>
@@ -1059,7 +1059,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_06.jpg</t>
+          <t>stimuli/bread/bread_07.jpg</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1079,7 +1079,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1127,7 +1127,7 @@
         <v>7</v>
       </c>
       <c r="T7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U7" t="n">
         <v>1</v>
@@ -1163,19 +1163,19 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>stimuli/hammer/hammer_44.jpg</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>stimuli/dog/dog_42.jpg</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
           <t>stimuli/bicycle/bicycle_17.jpg</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>stimuli/dog/dog_42.jpg</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>stimuli/flower/flower_49.jpg</t>
-        </is>
-      </c>
       <c r="I8" t="inlineStr">
         <is>
           <t>ball</t>
@@ -1183,17 +1183,17 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
+          <t>hammer</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>dog</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
           <t>bicycle</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>dog</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>flower</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1229,13 +1229,13 @@
         <v>1</v>
       </c>
       <c r="U8" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="V8" t="n">
         <v>5</v>
       </c>
       <c r="W8" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -1257,17 +1257,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_17.jpg</t>
+          <t>stimuli/hammer/hammer_44.jpg</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_44.jpg</t>
+          <t>stimuli/hand/hand_19.jpg</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_18.jpg</t>
+          <t>stimuli/chair/chair_06.jpg</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1277,17 +1277,17 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1325,13 +1325,13 @@
         <v>9</v>
       </c>
       <c r="T9" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="U9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V9" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="W9" t="n">
         <v>13</v>
@@ -1356,12 +1356,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_44.jpg</t>
+          <t>stimuli/hand/hand_19.jpg</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_18.jpg</t>
+          <t>stimuli/chair/chair_06.jpg</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1376,12 +1376,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1424,10 +1424,10 @@
         <v>10</v>
       </c>
       <c r="T10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U10" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="V10" t="n">
         <v>17</v>
@@ -1455,14 +1455,14 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
+          <t>stimuli/chair/chair_06.jpg</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
           <t>stimuli/jacket/jacket_18.jpg</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>stimuli/hand/hand_19.jpg</t>
-        </is>
-      </c>
       <c r="G11" t="inlineStr">
         <is>
           <t>stimuli/fish/fish_37.jpg</t>
@@ -1475,12 +1475,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
+          <t>chair</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>jacket</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>hand</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1523,10 +1523,10 @@
         <v>11</v>
       </c>
       <c r="T11" t="n">
+        <v>4</v>
+      </c>
+      <c r="U11" t="n">
         <v>10</v>
-      </c>
-      <c r="U11" t="n">
-        <v>8</v>
       </c>
       <c r="V11" t="n">
         <v>12</v>
@@ -1554,42 +1554,42 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_19.jpg</t>
+          <t>stimuli/jacket/jacket_18.jpg</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
+          <t>stimuli/flower/flower_49.jpg</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>stimuli/dog/dog_42.jpg</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
           <t>stimuli/bread/bread_07.jpg</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>stimuli/dog/dog_42.jpg</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>stimuli/chair/chair_06.jpg</t>
-        </is>
-      </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
+          <t>flower</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>dog</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
           <t>bread</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>dog</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>chair</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1622,16 +1622,16 @@
         <v>12</v>
       </c>
       <c r="T12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="V12" t="n">
         <v>5</v>
       </c>
       <c r="W12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_07.jpg</t>
+          <t>stimuli/flower/flower_49.jpg</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_17.jpg</t>
+          <t>stimuli/hammer/hammer_44.jpg</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1721,7 +1721,7 @@
         <v>13</v>
       </c>
       <c r="T13" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="U13" t="n">
         <v>17</v>
@@ -1730,7 +1730,7 @@
         <v>12</v>
       </c>
       <c r="W13" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_22.jpg</t>
+          <t>stimuli/hammer/hammer_13.jpg</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1881,7 +1881,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1925,7 +1925,7 @@
         <v>16</v>
       </c>
       <c r="V15" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="W15" t="n">
         <v>13</v>
@@ -1955,12 +1955,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_12.jpg</t>
+          <t>stimuli/chair/chair_49.jpg</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_34.jpg</t>
+          <t>stimuli/flower/flower_36.jpg</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1975,12 +1975,12 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -2021,10 +2021,10 @@
         <v>16</v>
       </c>
       <c r="U16" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="V16" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="W16" t="n">
         <v>14</v>
@@ -2049,42 +2049,42 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
+          <t>stimuli/chair/chair_49.jpg</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>stimuli/ball/ball_11.jpg</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
           <t>stimuli/jacket/jacket_12.jpg</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>stimuli/ball/ball_11.jpg</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>stimuli/hand/hand_34.jpg</t>
-        </is>
-      </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_36.jpg</t>
+          <t>stimuli/bicycle/bicycle_22.jpg</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
+          <t>chair</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>ball</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
           <t>jacket</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>ball</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>hand</t>
-        </is>
-      </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -2117,16 +2117,16 @@
         <v>4</v>
       </c>
       <c r="T17" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="U17" t="n">
         <v>1</v>
       </c>
       <c r="V17" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W17" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -2153,7 +2153,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_34.jpg</t>
+          <t>stimuli/flower/flower_36.jpg</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2173,7 +2173,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -2219,7 +2219,7 @@
         <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="V18" t="n">
         <v>5</v>
@@ -2247,14 +2247,14 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
+          <t>stimuli/flower/flower_36.jpg</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
           <t>stimuli/bread/bread_34.jpg</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>stimuli/chair/chair_49.jpg</t>
-        </is>
-      </c>
       <c r="G19" t="inlineStr">
         <is>
           <t>stimuli/house/house_48.jpg</t>
@@ -2262,19 +2262,19 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_36.jpg</t>
+          <t>stimuli/bicycle/bicycle_22.jpg</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
+          <t>flower</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
           <t>bread</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>chair</t>
-        </is>
-      </c>
       <c r="K19" t="inlineStr">
         <is>
           <t>house</t>
@@ -2282,7 +2282,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2315,16 +2315,16 @@
         <v>6</v>
       </c>
       <c r="T19" t="n">
+        <v>6</v>
+      </c>
+      <c r="U19" t="n">
         <v>3</v>
-      </c>
-      <c r="U19" t="n">
-        <v>4</v>
       </c>
       <c r="V19" t="n">
         <v>9</v>
       </c>
       <c r="W19" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -2346,7 +2346,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_49.jpg</t>
+          <t>stimuli/bread/bread_34.jpg</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2356,7 +2356,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_13.jpg</t>
+          <t>stimuli/hand/hand_34.jpg</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2366,7 +2366,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2414,13 +2414,13 @@
         <v>7</v>
       </c>
       <c r="T20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U20" t="n">
         <v>9</v>
       </c>
       <c r="V20" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W20" t="n">
         <v>13</v>
@@ -2450,7 +2450,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_34.jpg</t>
+          <t>stimuli/jacket/jacket_12.jpg</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -2516,7 +2516,7 @@
         <v>9</v>
       </c>
       <c r="U21" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V21" t="n">
         <v>16</v>
@@ -2544,14 +2544,14 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
+          <t>stimuli/jacket/jacket_12.jpg</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
           <t>stimuli/hand/hand_34.jpg</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>stimuli/hammer/hammer_13.jpg</t>
-        </is>
-      </c>
       <c r="G22" t="inlineStr">
         <is>
           <t>stimuli/ball/ball_11.jpg</t>
@@ -2559,19 +2559,19 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_49.jpg</t>
+          <t>stimuli/bread/bread_34.jpg</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
+          <t>jacket</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
           <t>hand</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>hammer</t>
-        </is>
-      </c>
       <c r="K22" t="inlineStr">
         <is>
           <t>ball</t>
@@ -2579,7 +2579,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2612,16 +2612,16 @@
         <v>9</v>
       </c>
       <c r="T22" t="n">
+        <v>10</v>
+      </c>
+      <c r="U22" t="n">
         <v>8</v>
-      </c>
-      <c r="U22" t="n">
-        <v>7</v>
       </c>
       <c r="V22" t="n">
         <v>1</v>
       </c>
       <c r="W22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23">
@@ -2643,7 +2643,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_13.jpg</t>
+          <t>stimuli/hand/hand_34.jpg</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2658,12 +2658,12 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_34.jpg</t>
+          <t>stimuli/flower/flower_36.jpg</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2678,7 +2678,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2711,7 +2711,7 @@
         <v>10</v>
       </c>
       <c r="T23" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U23" t="n">
         <v>5</v>
@@ -2720,7 +2720,7 @@
         <v>11</v>
       </c>
       <c r="W23" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24">
@@ -2747,17 +2747,17 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_22.jpg</t>
+          <t>stimuli/hammer/hammer_13.jpg</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_12.jpg</t>
+          <t>stimuli/chair/chair_49.jpg</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_49.jpg</t>
+          <t>stimuli/bread/bread_34.jpg</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2767,17 +2767,17 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2813,13 +2813,13 @@
         <v>5</v>
       </c>
       <c r="U24" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="V24" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="W24" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25">
@@ -2841,14 +2841,14 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
+          <t>stimuli/hammer/hammer_13.jpg</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
           <t>stimuli/bicycle/bicycle_22.jpg</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>stimuli/flower/flower_36.jpg</t>
-        </is>
-      </c>
       <c r="G25" t="inlineStr">
         <is>
           <t>stimuli/car/car_34.jpg</t>
@@ -2861,12 +2861,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
+          <t>hammer</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
           <t>bicycle</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>flower</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2909,10 +2909,10 @@
         <v>12</v>
       </c>
       <c r="T25" t="n">
+        <v>7</v>
+      </c>
+      <c r="U25" t="n">
         <v>2</v>
-      </c>
-      <c r="U25" t="n">
-        <v>6</v>
       </c>
       <c r="V25" t="n">
         <v>11</v>
@@ -2940,7 +2940,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_36.jpg</t>
+          <t>stimuli/bicycle/bicycle_22.jpg</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2955,12 +2955,12 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_49.jpg</t>
+          <t>stimuli/bread/bread_34.jpg</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2975,7 +2975,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -3008,7 +3008,7 @@
         <v>13</v>
       </c>
       <c r="T26" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="U26" t="n">
         <v>14</v>
@@ -3017,7 +3017,7 @@
         <v>1</v>
       </c>
       <c r="W26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27">
@@ -3054,7 +3054,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_34.jpg</t>
+          <t>stimuli/jacket/jacket_12.jpg</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3074,7 +3074,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -3116,7 +3116,7 @@
         <v>16</v>
       </c>
       <c r="W27" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28">
@@ -3148,7 +3148,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_07.jpg</t>
+          <t>stimuli/flower/flower_49.jpg</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3168,7 +3168,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -3212,7 +3212,7 @@
         <v>13</v>
       </c>
       <c r="V28" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="W28" t="n">
         <v>14</v>
@@ -3346,7 +3346,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_17.jpg</t>
+          <t>stimuli/hammer/hammer_44.jpg</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -3410,7 +3410,7 @@
         <v>9</v>
       </c>
       <c r="V30" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="W30" t="n">
         <v>14</v>
@@ -3440,7 +3440,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_49.jpg</t>
+          <t>stimuli/bicycle/bicycle_17.jpg</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -3460,7 +3460,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -3506,7 +3506,7 @@
         <v>9</v>
       </c>
       <c r="U31" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="V31" t="n">
         <v>1</v>
@@ -3534,17 +3534,17 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_49.jpg</t>
+          <t>stimuli/bicycle/bicycle_17.jpg</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_06.jpg</t>
+          <t>stimuli/bread/bread_07.jpg</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_19.jpg</t>
+          <t>stimuli/jacket/jacket_18.jpg</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3554,17 +3554,17 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -3602,13 +3602,13 @@
         <v>6</v>
       </c>
       <c r="T32" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="U32" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V32" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W32" t="n">
         <v>17</v>
@@ -3633,19 +3633,19 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
+          <t>stimuli/bread/bread_07.jpg</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>stimuli/ball/ball_06.jpg</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
           <t>stimuli/chair/chair_06.jpg</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>stimuli/ball/ball_06.jpg</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>stimuli/jacket/jacket_18.jpg</t>
-        </is>
-      </c>
       <c r="H33" t="inlineStr">
         <is>
           <t>stimuli/lamp/lamp_22.jpg</t>
@@ -3653,17 +3653,17 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
+          <t>bread</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>ball</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
           <t>chair</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>ball</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>jacket</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -3701,13 +3701,13 @@
         <v>7</v>
       </c>
       <c r="T33" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U33" t="n">
         <v>1</v>
       </c>
       <c r="V33" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="W33" t="n">
         <v>14</v>
@@ -3737,19 +3737,19 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
+          <t>stimuli/hammer/hammer_44.jpg</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>stimuli/lamp/lamp_22.jpg</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
           <t>stimuli/bicycle/bicycle_17.jpg</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>stimuli/lamp/lamp_22.jpg</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>stimuli/flower/flower_49.jpg</t>
-        </is>
-      </c>
       <c r="I34" t="inlineStr">
         <is>
           <t>ball</t>
@@ -3757,17 +3757,17 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
+          <t>hammer</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>lamp</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
           <t>bicycle</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>lamp</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>flower</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -3803,13 +3803,13 @@
         <v>1</v>
       </c>
       <c r="U34" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="V34" t="n">
         <v>14</v>
       </c>
       <c r="W34" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35">
@@ -3831,12 +3831,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_17.jpg</t>
+          <t>stimuli/hammer/hammer_44.jpg</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_44.jpg</t>
+          <t>stimuli/hand/hand_19.jpg</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -3846,17 +3846,17 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_06.jpg</t>
+          <t>stimuli/bread/bread_07.jpg</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -3899,16 +3899,16 @@
         <v>9</v>
       </c>
       <c r="T35" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="U35" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V35" t="n">
         <v>13</v>
       </c>
       <c r="W35" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36">
@@ -3930,12 +3930,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_44.jpg</t>
+          <t>stimuli/hand/hand_19.jpg</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_18.jpg</t>
+          <t>stimuli/chair/chair_06.jpg</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -3950,12 +3950,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -3998,10 +3998,10 @@
         <v>10</v>
       </c>
       <c r="T36" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U36" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="V36" t="n">
         <v>5</v>
@@ -4029,17 +4029,17 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
+          <t>stimuli/chair/chair_06.jpg</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
           <t>stimuli/jacket/jacket_18.jpg</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>stimuli/hand/hand_19.jpg</t>
-        </is>
-      </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_07.jpg</t>
+          <t>stimuli/flower/flower_49.jpg</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -4049,17 +4049,17 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
+          <t>chair</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
           <t>jacket</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>hand</t>
-        </is>
-      </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -4097,13 +4097,13 @@
         <v>11</v>
       </c>
       <c r="T37" t="n">
+        <v>4</v>
+      </c>
+      <c r="U37" t="n">
         <v>10</v>
       </c>
-      <c r="U37" t="n">
-        <v>8</v>
-      </c>
       <c r="V37" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="W37" t="n">
         <v>14</v>
@@ -4128,42 +4128,42 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
+          <t>stimuli/jacket/jacket_18.jpg</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>stimuli/flower/flower_49.jpg</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>stimuli/fish/fish_37.jpg</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
           <t>stimuli/hand/hand_19.jpg</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>stimuli/bread/bread_07.jpg</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>stimuli/fish/fish_37.jpg</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>stimuli/hammer/hammer_44.jpg</t>
-        </is>
-      </c>
       <c r="I38" t="inlineStr">
         <is>
+          <t>jacket</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>flower</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>fish</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
           <t>hand</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>bread</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>fish</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>hammer</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -4196,16 +4196,16 @@
         <v>12</v>
       </c>
       <c r="T38" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U38" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="V38" t="n">
         <v>12</v>
       </c>
       <c r="W38" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="39">
@@ -4227,7 +4227,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_07.jpg</t>
+          <t>stimuli/flower/flower_49.jpg</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -4242,12 +4242,12 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_49.jpg</t>
+          <t>stimuli/bicycle/bicycle_17.jpg</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -4262,7 +4262,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -4295,7 +4295,7 @@
         <v>13</v>
       </c>
       <c r="T39" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="U39" t="n">
         <v>17</v>
@@ -4304,7 +4304,7 @@
         <v>5</v>
       </c>
       <c r="W39" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -4529,7 +4529,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_12.jpg</t>
+          <t>stimuli/chair/chair_49.jpg</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -4549,7 +4549,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -4595,7 +4595,7 @@
         <v>16</v>
       </c>
       <c r="U42" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="V42" t="n">
         <v>5</v>
@@ -4623,7 +4623,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_12.jpg</t>
+          <t>stimuli/chair/chair_49.jpg</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -4633,7 +4633,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_22.jpg</t>
+          <t>stimuli/hammer/hammer_13.jpg</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -4643,7 +4643,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -4653,7 +4653,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -4691,13 +4691,13 @@
         <v>4</v>
       </c>
       <c r="T43" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="U43" t="n">
         <v>1</v>
       </c>
       <c r="V43" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="W43" t="n">
         <v>14</v>
@@ -4727,17 +4727,17 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
+          <t>stimuli/flower/flower_36.jpg</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
           <t>stimuli/bread/bread_34.jpg</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>stimuli/chair/chair_49.jpg</t>
-        </is>
-      </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_36.jpg</t>
+          <t>stimuli/bicycle/bicycle_22.jpg</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -4747,17 +4747,17 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
+          <t>flower</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
           <t>bread</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>chair</t>
-        </is>
-      </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -4793,13 +4793,13 @@
         <v>1</v>
       </c>
       <c r="U44" t="n">
+        <v>6</v>
+      </c>
+      <c r="V44" t="n">
         <v>3</v>
       </c>
-      <c r="V44" t="n">
-        <v>4</v>
-      </c>
       <c r="W44" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45">
@@ -4821,42 +4821,42 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
+          <t>stimuli/flower/flower_36.jpg</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
           <t>stimuli/bread/bread_34.jpg</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>stimuli/car/car_34.jpg</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
         <is>
           <t>stimuli/chair/chair_49.jpg</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>stimuli/car/car_34.jpg</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>stimuli/jacket/jacket_12.jpg</t>
-        </is>
-      </c>
       <c r="I45" t="inlineStr">
         <is>
+          <t>flower</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
           <t>bread</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr">
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>car</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
         <is>
           <t>chair</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>car</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>jacket</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -4889,16 +4889,16 @@
         <v>6</v>
       </c>
       <c r="T45" t="n">
+        <v>6</v>
+      </c>
+      <c r="U45" t="n">
         <v>3</v>
-      </c>
-      <c r="U45" t="n">
-        <v>4</v>
       </c>
       <c r="V45" t="n">
         <v>11</v>
       </c>
       <c r="W45" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="46">
@@ -4920,7 +4920,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_49.jpg</t>
+          <t>stimuli/bread/bread_34.jpg</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -4930,7 +4930,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_13.jpg</t>
+          <t>stimuli/hand/hand_34.jpg</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -4940,7 +4940,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -4950,7 +4950,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -4988,13 +4988,13 @@
         <v>7</v>
       </c>
       <c r="T46" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U46" t="n">
         <v>9</v>
       </c>
       <c r="V46" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W46" t="n">
         <v>13</v>
@@ -5024,17 +5024,17 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_34.jpg</t>
+          <t>stimuli/jacket/jacket_12.jpg</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_12.jpg</t>
+          <t>stimuli/chair/chair_49.jpg</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_34.jpg</t>
+          <t>stimuli/flower/flower_36.jpg</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -5044,17 +5044,17 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -5090,13 +5090,13 @@
         <v>9</v>
       </c>
       <c r="U47" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V47" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="W47" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="48">
@@ -5118,14 +5118,14 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
+          <t>stimuli/jacket/jacket_12.jpg</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
           <t>stimuli/hand/hand_34.jpg</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>stimuli/hammer/hammer_13.jpg</t>
-        </is>
-      </c>
       <c r="G48" t="inlineStr">
         <is>
           <t>stimuli/lamp/lamp_13.jpg</t>
@@ -5138,12 +5138,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
+          <t>jacket</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
           <t>hand</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>hammer</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -5186,10 +5186,10 @@
         <v>9</v>
       </c>
       <c r="T48" t="n">
+        <v>10</v>
+      </c>
+      <c r="U48" t="n">
         <v>8</v>
-      </c>
-      <c r="U48" t="n">
-        <v>7</v>
       </c>
       <c r="V48" t="n">
         <v>14</v>
@@ -5217,7 +5217,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_13.jpg</t>
+          <t>stimuli/hand/hand_34.jpg</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -5237,7 +5237,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -5285,7 +5285,7 @@
         <v>10</v>
       </c>
       <c r="T49" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U49" t="n">
         <v>5</v>
@@ -5321,7 +5321,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_22.jpg</t>
+          <t>stimuli/hammer/hammer_13.jpg</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -5331,7 +5331,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_34.jpg</t>
+          <t>stimuli/jacket/jacket_12.jpg</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -5341,7 +5341,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -5387,13 +5387,13 @@
         <v>5</v>
       </c>
       <c r="U50" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="V50" t="n">
         <v>11</v>
       </c>
       <c r="W50" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="51">
@@ -5415,14 +5415,14 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
+          <t>stimuli/hammer/hammer_13.jpg</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
           <t>stimuli/bicycle/bicycle_22.jpg</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>stimuli/flower/flower_36.jpg</t>
-        </is>
-      </c>
       <c r="G51" t="inlineStr">
         <is>
           <t>stimuli/guitar/guitar_12.jpg</t>
@@ -5435,12 +5435,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
+          <t>hammer</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
           <t>bicycle</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>flower</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -5483,10 +5483,10 @@
         <v>12</v>
       </c>
       <c r="T51" t="n">
+        <v>7</v>
+      </c>
+      <c r="U51" t="n">
         <v>2</v>
-      </c>
-      <c r="U51" t="n">
-        <v>6</v>
       </c>
       <c r="V51" t="n">
         <v>13</v>
@@ -5514,42 +5514,42 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
+          <t>stimuli/bicycle/bicycle_22.jpg</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>stimuli/lamp/lamp_13.jpg</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>stimuli/car/car_34.jpg</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
           <t>stimuli/flower/flower_36.jpg</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>stimuli/lamp/lamp_13.jpg</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>stimuli/car/car_34.jpg</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>stimuli/bread/bread_34.jpg</t>
-        </is>
-      </c>
       <c r="I52" t="inlineStr">
         <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>lamp</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>car</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
           <t>flower</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>lamp</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>car</t>
-        </is>
-      </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>bread</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -5582,7 +5582,7 @@
         <v>13</v>
       </c>
       <c r="T52" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="U52" t="n">
         <v>14</v>
@@ -5591,7 +5591,7 @@
         <v>11</v>
       </c>
       <c r="W52" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="53">
@@ -5821,7 +5821,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_07.jpg</t>
+          <t>stimuli/flower/flower_49.jpg</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -5841,7 +5841,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -5885,7 +5885,7 @@
         <v>5</v>
       </c>
       <c r="V55" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="W55" t="n">
         <v>14</v>
@@ -5920,7 +5920,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_18.jpg</t>
+          <t>stimuli/chair/chair_06.jpg</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -5940,7 +5940,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -5984,7 +5984,7 @@
         <v>9</v>
       </c>
       <c r="V56" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="W56" t="n">
         <v>17</v>
@@ -6014,12 +6014,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_49.jpg</t>
+          <t>stimuli/bicycle/bicycle_17.jpg</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_06.jpg</t>
+          <t>stimuli/bread/bread_07.jpg</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -6080,10 +6080,10 @@
         <v>9</v>
       </c>
       <c r="U57" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="V57" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W57" t="n">
         <v>14</v>
@@ -6108,42 +6108,42 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_49.jpg</t>
+          <t>stimuli/bicycle/bicycle_17.jpg</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_06.jpg</t>
+          <t>stimuli/bread/bread_07.jpg</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_44.jpg</t>
+          <t>stimuli/hand/hand_19.jpg</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_19.jpg</t>
+          <t>stimuli/jacket/jacket_18.jpg</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -6176,16 +6176,16 @@
         <v>6</v>
       </c>
       <c r="T58" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="U58" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V58" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W58" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="59">
@@ -6207,7 +6207,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_06.jpg</t>
+          <t>stimuli/bread/bread_07.jpg</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -6217,7 +6217,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_17.jpg</t>
+          <t>stimuli/hammer/hammer_44.jpg</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -6227,7 +6227,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -6237,7 +6237,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -6275,13 +6275,13 @@
         <v>7</v>
       </c>
       <c r="T59" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U59" t="n">
         <v>1</v>
       </c>
       <c r="V59" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="W59" t="n">
         <v>17</v>
@@ -6311,19 +6311,19 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
+          <t>stimuli/hammer/hammer_44.jpg</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>stimuli/guitar/guitar_07.jpg</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
           <t>stimuli/bicycle/bicycle_17.jpg</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>stimuli/guitar/guitar_07.jpg</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>stimuli/flower/flower_49.jpg</t>
-        </is>
-      </c>
       <c r="I60" t="inlineStr">
         <is>
           <t>ball</t>
@@ -6331,17 +6331,17 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
+          <t>hammer</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>guitar</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
           <t>bicycle</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>guitar</t>
-        </is>
-      </c>
-      <c r="L60" t="inlineStr">
-        <is>
-          <t>flower</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -6377,13 +6377,13 @@
         <v>1</v>
       </c>
       <c r="U60" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="V60" t="n">
         <v>13</v>
       </c>
       <c r="W60" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61">
@@ -6405,12 +6405,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_17.jpg</t>
+          <t>stimuli/hammer/hammer_44.jpg</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_44.jpg</t>
+          <t>stimuli/hand/hand_19.jpg</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -6420,17 +6420,17 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_06.jpg</t>
+          <t>stimuli/bread/bread_07.jpg</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -6440,7 +6440,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -6473,16 +6473,16 @@
         <v>9</v>
       </c>
       <c r="T61" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="U61" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V61" t="n">
         <v>9</v>
       </c>
       <c r="W61" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="62">
@@ -6504,12 +6504,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_44.jpg</t>
+          <t>stimuli/hand/hand_19.jpg</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_18.jpg</t>
+          <t>stimuli/chair/chair_06.jpg</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -6572,10 +6572,10 @@
         <v>10</v>
       </c>
       <c r="T62" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U62" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="V62" t="n">
         <v>13</v>
@@ -6603,14 +6603,14 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
+          <t>stimuli/chair/chair_06.jpg</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
           <t>stimuli/jacket/jacket_18.jpg</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>stimuli/hand/hand_19.jpg</t>
-        </is>
-      </c>
       <c r="G63" t="inlineStr">
         <is>
           <t>stimuli/fish/fish_37.jpg</t>
@@ -6618,19 +6618,19 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_06.jpg</t>
+          <t>stimuli/bread/bread_07.jpg</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
+          <t>chair</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
           <t>jacket</t>
         </is>
       </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>hand</t>
-        </is>
-      </c>
       <c r="K63" t="inlineStr">
         <is>
           <t>fish</t>
@@ -6638,7 +6638,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -6671,16 +6671,16 @@
         <v>11</v>
       </c>
       <c r="T63" t="n">
+        <v>4</v>
+      </c>
+      <c r="U63" t="n">
         <v>10</v>
-      </c>
-      <c r="U63" t="n">
-        <v>8</v>
       </c>
       <c r="V63" t="n">
         <v>12</v>
       </c>
       <c r="W63" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="64">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_19.jpg</t>
+          <t>stimuli/jacket/jacket_18.jpg</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_07.jpg</t>
+          <t>stimuli/flower/flower_49.jpg</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -6717,17 +6717,17 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_17.jpg</t>
+          <t>stimuli/hammer/hammer_44.jpg</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -6737,7 +6737,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -6770,16 +6770,16 @@
         <v>12</v>
       </c>
       <c r="T64" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U64" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="V64" t="n">
         <v>5</v>
       </c>
       <c r="W64" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="65">
@@ -6801,7 +6801,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_07.jpg</t>
+          <t>stimuli/flower/flower_49.jpg</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -6821,7 +6821,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -6869,7 +6869,7 @@
         <v>13</v>
       </c>
       <c r="T65" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="U65" t="n">
         <v>17</v>
@@ -6915,7 +6915,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_49.jpg</t>
+          <t>stimuli/bicycle/bicycle_17.jpg</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6935,7 +6935,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -6977,7 +6977,7 @@
         <v>5</v>
       </c>
       <c r="W66" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="67">
@@ -7009,7 +7009,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_34.jpg</t>
+          <t>stimuli/jacket/jacket_12.jpg</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -7029,7 +7029,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -7073,7 +7073,7 @@
         <v>16</v>
       </c>
       <c r="V67" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W67" t="n">
         <v>13</v>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_12.jpg</t>
+          <t>stimuli/chair/chair_49.jpg</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_49.jpg</t>
+          <t>stimuli/bread/bread_34.jpg</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -7169,10 +7169,10 @@
         <v>16</v>
       </c>
       <c r="U68" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="V68" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W68" t="n">
         <v>14</v>
@@ -7197,42 +7197,42 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
+          <t>stimuli/chair/chair_49.jpg</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>stimuli/ball/ball_11.jpg</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
           <t>stimuli/jacket/jacket_12.jpg</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>stimuli/ball/ball_11.jpg</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>stimuli/hand/hand_34.jpg</t>
-        </is>
-      </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_36.jpg</t>
+          <t>stimuli/bicycle/bicycle_22.jpg</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
+          <t>chair</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>ball</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
           <t>jacket</t>
         </is>
       </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>ball</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>hand</t>
-        </is>
-      </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -7265,16 +7265,16 @@
         <v>4</v>
       </c>
       <c r="T69" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="U69" t="n">
         <v>1</v>
       </c>
       <c r="V69" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W69" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70">
@@ -7301,7 +7301,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_34.jpg</t>
+          <t>stimuli/flower/flower_36.jpg</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -7321,7 +7321,7 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -7367,7 +7367,7 @@
         <v>1</v>
       </c>
       <c r="U70" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="V70" t="n">
         <v>9</v>
@@ -7395,14 +7395,14 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
+          <t>stimuli/flower/flower_36.jpg</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
           <t>stimuli/bread/bread_34.jpg</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>stimuli/chair/chair_49.jpg</t>
-        </is>
-      </c>
       <c r="G71" t="inlineStr">
         <is>
           <t>stimuli/dog/dog_19.jpg</t>
@@ -7415,12 +7415,12 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
+          <t>flower</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
           <t>bread</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>chair</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -7463,10 +7463,10 @@
         <v>6</v>
       </c>
       <c r="T71" t="n">
+        <v>6</v>
+      </c>
+      <c r="U71" t="n">
         <v>3</v>
-      </c>
-      <c r="U71" t="n">
-        <v>4</v>
       </c>
       <c r="V71" t="n">
         <v>5</v>
@@ -7494,42 +7494,42 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
+          <t>stimuli/bread/bread_34.jpg</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>stimuli/house/house_48.jpg</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>stimuli/car/car_34.jpg</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
           <t>stimuli/chair/chair_49.jpg</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>stimuli/house/house_48.jpg</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>stimuli/car/car_34.jpg</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>stimuli/jacket/jacket_12.jpg</t>
-        </is>
-      </c>
       <c r="I72" t="inlineStr">
         <is>
+          <t>bread</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>house</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>car</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
           <t>chair</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>house</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>car</t>
-        </is>
-      </c>
-      <c r="L72" t="inlineStr">
-        <is>
-          <t>jacket</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -7562,7 +7562,7 @@
         <v>7</v>
       </c>
       <c r="T72" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U72" t="n">
         <v>9</v>
@@ -7571,7 +7571,7 @@
         <v>11</v>
       </c>
       <c r="W72" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="73">
@@ -7598,14 +7598,14 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
+          <t>stimuli/jacket/jacket_12.jpg</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
           <t>stimuli/hand/hand_34.jpg</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>stimuli/hammer/hammer_13.jpg</t>
-        </is>
-      </c>
       <c r="H73" t="inlineStr">
         <is>
           <t>stimuli/lamp/lamp_13.jpg</t>
@@ -7618,12 +7618,12 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
+          <t>jacket</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
           <t>hand</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>hammer</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -7664,10 +7664,10 @@
         <v>9</v>
       </c>
       <c r="U73" t="n">
+        <v>10</v>
+      </c>
+      <c r="V73" t="n">
         <v>8</v>
-      </c>
-      <c r="V73" t="n">
-        <v>7</v>
       </c>
       <c r="W73" t="n">
         <v>14</v>
@@ -7692,42 +7692,42 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
+          <t>stimuli/jacket/jacket_12.jpg</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
           <t>stimuli/hand/hand_34.jpg</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>stimuli/hammer/hammer_13.jpg</t>
-        </is>
-      </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_12.jpg</t>
+          <t>stimuli/chair/chair_49.jpg</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_34.jpg</t>
+          <t>stimuli/flower/flower_36.jpg</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
+          <t>jacket</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
           <t>hand</t>
         </is>
       </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>hammer</t>
-        </is>
-      </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -7760,16 +7760,16 @@
         <v>9</v>
       </c>
       <c r="T74" t="n">
+        <v>10</v>
+      </c>
+      <c r="U74" t="n">
         <v>8</v>
       </c>
-      <c r="U74" t="n">
-        <v>7</v>
-      </c>
       <c r="V74" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="W74" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="75">
@@ -7791,19 +7791,19 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
+          <t>stimuli/hand/hand_34.jpg</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>stimuli/dog/dog_19.jpg</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
           <t>stimuli/hammer/hammer_13.jpg</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>stimuli/dog/dog_19.jpg</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>stimuli/bicycle/bicycle_22.jpg</t>
-        </is>
-      </c>
       <c r="H75" t="inlineStr">
         <is>
           <t>stimuli/guitar/guitar_12.jpg</t>
@@ -7811,17 +7811,17 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
+          <t>hand</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>dog</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
           <t>hammer</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>dog</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>bicycle</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -7859,13 +7859,13 @@
         <v>10</v>
       </c>
       <c r="T75" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U75" t="n">
         <v>5</v>
       </c>
       <c r="V75" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="W75" t="n">
         <v>13</v>
@@ -7895,7 +7895,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_22.jpg</t>
+          <t>stimuli/hammer/hammer_13.jpg</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -7905,7 +7905,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_34.jpg</t>
+          <t>stimuli/flower/flower_36.jpg</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -7915,7 +7915,7 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -7925,7 +7925,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -7961,13 +7961,13 @@
         <v>5</v>
       </c>
       <c r="U76" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="V76" t="n">
         <v>16</v>
       </c>
       <c r="W76" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="77">
@@ -7989,14 +7989,14 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
+          <t>stimuli/hammer/hammer_13.jpg</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
           <t>stimuli/bicycle/bicycle_22.jpg</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>stimuli/flower/flower_36.jpg</t>
-        </is>
-      </c>
       <c r="G77" t="inlineStr">
         <is>
           <t>stimuli/ball/ball_11.jpg</t>
@@ -8004,19 +8004,19 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_34.jpg</t>
+          <t>stimuli/jacket/jacket_12.jpg</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
+          <t>hammer</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
           <t>bicycle</t>
         </is>
       </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>flower</t>
-        </is>
-      </c>
       <c r="K77" t="inlineStr">
         <is>
           <t>ball</t>
@@ -8024,7 +8024,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -8057,16 +8057,16 @@
         <v>12</v>
       </c>
       <c r="T77" t="n">
+        <v>7</v>
+      </c>
+      <c r="U77" t="n">
         <v>2</v>
-      </c>
-      <c r="U77" t="n">
-        <v>6</v>
       </c>
       <c r="V77" t="n">
         <v>1</v>
       </c>
       <c r="W77" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="78">
@@ -8088,7 +8088,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_36.jpg</t>
+          <t>stimuli/bicycle/bicycle_22.jpg</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -8103,12 +8103,12 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_12.jpg</t>
+          <t>stimuli/chair/chair_49.jpg</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -8123,7 +8123,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -8156,7 +8156,7 @@
         <v>13</v>
       </c>
       <c r="T78" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="U78" t="n">
         <v>14</v>
@@ -8165,7 +8165,7 @@
         <v>11</v>
       </c>
       <c r="W78" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="79">
@@ -8197,7 +8197,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_34.jpg</t>
+          <t>stimuli/jacket/jacket_12.jpg</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -8217,7 +8217,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -8261,7 +8261,7 @@
         <v>13</v>
       </c>
       <c r="V79" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W79" t="n">
         <v>11</v>
@@ -8395,7 +8395,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_49.jpg</t>
+          <t>stimuli/bicycle/bicycle_17.jpg</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -8415,7 +8415,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -8459,7 +8459,7 @@
         <v>5</v>
       </c>
       <c r="V81" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="W81" t="n">
         <v>17</v>
@@ -8494,7 +8494,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_44.jpg</t>
+          <t>stimuli/hand/hand_19.jpg</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -8514,7 +8514,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -8558,7 +8558,7 @@
         <v>9</v>
       </c>
       <c r="V82" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W82" t="n">
         <v>14</v>
@@ -8588,12 +8588,12 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_49.jpg</t>
+          <t>stimuli/bicycle/bicycle_17.jpg</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_19.jpg</t>
+          <t>stimuli/jacket/jacket_18.jpg</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -8608,12 +8608,12 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -8654,10 +8654,10 @@
         <v>9</v>
       </c>
       <c r="U83" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="V83" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W83" t="n">
         <v>17</v>
@@ -8682,42 +8682,42 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
+          <t>stimuli/bicycle/bicycle_17.jpg</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>stimuli/bread/bread_07.jpg</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>stimuli/chair/chair_06.jpg</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
           <t>stimuli/flower/flower_49.jpg</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>stimuli/chair/chair_06.jpg</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>stimuli/jacket/jacket_18.jpg</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>stimuli/bread/bread_07.jpg</t>
-        </is>
-      </c>
       <c r="I84" t="inlineStr">
         <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>bread</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>chair</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
           <t>flower</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>chair</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>jacket</t>
-        </is>
-      </c>
-      <c r="L84" t="inlineStr">
-        <is>
-          <t>bread</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -8750,16 +8750,16 @@
         <v>6</v>
       </c>
       <c r="T84" t="n">
+        <v>2</v>
+      </c>
+      <c r="U84" t="n">
+        <v>3</v>
+      </c>
+      <c r="V84" t="n">
+        <v>4</v>
+      </c>
+      <c r="W84" t="n">
         <v>6</v>
-      </c>
-      <c r="U84" t="n">
-        <v>4</v>
-      </c>
-      <c r="V84" t="n">
-        <v>10</v>
-      </c>
-      <c r="W84" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="85">
@@ -8781,7 +8781,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_06.jpg</t>
+          <t>stimuli/bread/bread_07.jpg</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -8791,7 +8791,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_17.jpg</t>
+          <t>stimuli/hammer/hammer_44.jpg</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -8801,7 +8801,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -8811,7 +8811,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -8849,13 +8849,13 @@
         <v>7</v>
       </c>
       <c r="T85" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U85" t="n">
         <v>1</v>
       </c>
       <c r="V85" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="W85" t="n">
         <v>14</v>
@@ -8885,12 +8885,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_17.jpg</t>
+          <t>stimuli/hammer/hammer_44.jpg</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_07.jpg</t>
+          <t>stimuli/flower/flower_49.jpg</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -8905,12 +8905,12 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -8951,10 +8951,10 @@
         <v>1</v>
       </c>
       <c r="U86" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="V86" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="W86" t="n">
         <v>12</v>
@@ -8979,12 +8979,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_17.jpg</t>
+          <t>stimuli/hammer/hammer_44.jpg</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_44.jpg</t>
+          <t>stimuli/hand/hand_19.jpg</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -8994,17 +8994,17 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_06.jpg</t>
+          <t>stimuli/bread/bread_07.jpg</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -9014,7 +9014,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
@@ -9047,16 +9047,16 @@
         <v>9</v>
       </c>
       <c r="T87" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="U87" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V87" t="n">
         <v>9</v>
       </c>
       <c r="W87" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="88">
@@ -9078,12 +9078,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_44.jpg</t>
+          <t>stimuli/hand/hand_19.jpg</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_18.jpg</t>
+          <t>stimuli/chair/chair_06.jpg</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -9098,12 +9098,12 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -9146,10 +9146,10 @@
         <v>10</v>
       </c>
       <c r="T88" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U88" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="V88" t="n">
         <v>12</v>
@@ -9177,14 +9177,14 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
+          <t>stimuli/chair/chair_06.jpg</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
           <t>stimuli/jacket/jacket_18.jpg</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>stimuli/hand/hand_19.jpg</t>
-        </is>
-      </c>
       <c r="G89" t="inlineStr">
         <is>
           <t>stimuli/guitar/guitar_07.jpg</t>
@@ -9197,12 +9197,12 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
+          <t>chair</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
           <t>jacket</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>hand</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -9245,10 +9245,10 @@
         <v>11</v>
       </c>
       <c r="T89" t="n">
+        <v>4</v>
+      </c>
+      <c r="U89" t="n">
         <v>10</v>
-      </c>
-      <c r="U89" t="n">
-        <v>8</v>
       </c>
       <c r="V89" t="n">
         <v>13</v>
@@ -9276,12 +9276,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_19.jpg</t>
+          <t>stimuli/jacket/jacket_18.jpg</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_07.jpg</t>
+          <t>stimuli/flower/flower_49.jpg</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -9291,17 +9291,17 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_17.jpg</t>
+          <t>stimuli/hammer/hammer_44.jpg</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -9311,7 +9311,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -9344,16 +9344,16 @@
         <v>12</v>
       </c>
       <c r="T90" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U90" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="V90" t="n">
         <v>12</v>
       </c>
       <c r="W90" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="91">
@@ -9375,7 +9375,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_07.jpg</t>
+          <t>stimuli/flower/flower_49.jpg</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -9390,12 +9390,12 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_44.jpg</t>
+          <t>stimuli/hand/hand_19.jpg</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -9410,7 +9410,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -9443,7 +9443,7 @@
         <v>13</v>
       </c>
       <c r="T91" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="U91" t="n">
         <v>17</v>
@@ -9452,7 +9452,7 @@
         <v>5</v>
       </c>
       <c r="W91" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="92">
@@ -9489,7 +9489,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_19.jpg</t>
+          <t>stimuli/jacket/jacket_18.jpg</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -9509,7 +9509,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -9551,7 +9551,7 @@
         <v>13</v>
       </c>
       <c r="W92" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="93">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_12.jpg</t>
+          <t>stimuli/chair/chair_49.jpg</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_13.jpg</t>
+          <t>stimuli/hand/hand_34.jpg</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -9697,12 +9697,12 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -9743,10 +9743,10 @@
         <v>16</v>
       </c>
       <c r="U94" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="V94" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W94" t="n">
         <v>14</v>
@@ -9771,7 +9771,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_12.jpg</t>
+          <t>stimuli/chair/chair_49.jpg</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -9781,7 +9781,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_22.jpg</t>
+          <t>stimuli/hammer/hammer_13.jpg</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -9791,7 +9791,7 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -9839,13 +9839,13 @@
         <v>4</v>
       </c>
       <c r="T95" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="U95" t="n">
         <v>1</v>
       </c>
       <c r="V95" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="W95" t="n">
         <v>13</v>
@@ -9875,12 +9875,12 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_34.jpg</t>
+          <t>stimuli/flower/flower_36.jpg</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_34.jpg</t>
+          <t>stimuli/jacket/jacket_12.jpg</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -9895,12 +9895,12 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -9941,10 +9941,10 @@
         <v>1</v>
       </c>
       <c r="U96" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="V96" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W96" t="n">
         <v>14</v>
@@ -9969,17 +9969,17 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
+          <t>stimuli/flower/flower_36.jpg</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
           <t>stimuli/bread/bread_34.jpg</t>
         </is>
       </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>stimuli/chair/chair_49.jpg</t>
-        </is>
-      </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_13.jpg</t>
+          <t>stimuli/hand/hand_34.jpg</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -9989,17 +9989,17 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
+          <t>flower</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
           <t>bread</t>
         </is>
       </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>chair</t>
-        </is>
-      </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -10037,13 +10037,13 @@
         <v>6</v>
       </c>
       <c r="T97" t="n">
+        <v>6</v>
+      </c>
+      <c r="U97" t="n">
         <v>3</v>
       </c>
-      <c r="U97" t="n">
-        <v>4</v>
-      </c>
       <c r="V97" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W97" t="n">
         <v>16</v>
@@ -10068,7 +10068,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_49.jpg</t>
+          <t>stimuli/bread/bread_34.jpg</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -10078,7 +10078,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_36.jpg</t>
+          <t>stimuli/bicycle/bicycle_22.jpg</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -10088,7 +10088,7 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -10098,7 +10098,7 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -10136,13 +10136,13 @@
         <v>7</v>
       </c>
       <c r="T98" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U98" t="n">
         <v>9</v>
       </c>
       <c r="V98" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="W98" t="n">
         <v>13</v>
@@ -10172,7 +10172,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_34.jpg</t>
+          <t>stimuli/jacket/jacket_12.jpg</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -10192,7 +10192,7 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -10238,7 +10238,7 @@
         <v>9</v>
       </c>
       <c r="U99" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V99" t="n">
         <v>5</v>
@@ -10266,42 +10266,42 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
+          <t>stimuli/jacket/jacket_12.jpg</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
           <t>stimuli/hand/hand_34.jpg</t>
         </is>
       </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>stimuli/hammer/hammer_13.jpg</t>
-        </is>
-      </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_12.jpg</t>
+          <t>stimuli/chair/chair_49.jpg</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_34.jpg</t>
+          <t>stimuli/flower/flower_36.jpg</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
+          <t>jacket</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
           <t>hand</t>
         </is>
       </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>hammer</t>
-        </is>
-      </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
@@ -10334,16 +10334,16 @@
         <v>9</v>
       </c>
       <c r="T100" t="n">
+        <v>10</v>
+      </c>
+      <c r="U100" t="n">
         <v>8</v>
       </c>
-      <c r="U100" t="n">
-        <v>7</v>
-      </c>
       <c r="V100" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="W100" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="101">
@@ -10365,7 +10365,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_13.jpg</t>
+          <t>stimuli/hand/hand_34.jpg</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -10385,7 +10385,7 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -10433,7 +10433,7 @@
         <v>10</v>
       </c>
       <c r="T101" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U101" t="n">
         <v>5</v>
@@ -10469,7 +10469,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_22.jpg</t>
+          <t>stimuli/hammer/hammer_13.jpg</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -10479,7 +10479,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_34.jpg</t>
+          <t>stimuli/flower/flower_36.jpg</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -10489,7 +10489,7 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>bicycle</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -10499,7 +10499,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
@@ -10535,13 +10535,13 @@
         <v>5</v>
       </c>
       <c r="U102" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="V102" t="n">
         <v>11</v>
       </c>
       <c r="W102" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="103">
@@ -10563,14 +10563,14 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
+          <t>stimuli/hammer/hammer_13.jpg</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
           <t>stimuli/bicycle/bicycle_22.jpg</t>
         </is>
       </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>stimuli/flower/flower_36.jpg</t>
-        </is>
-      </c>
       <c r="G103" t="inlineStr">
         <is>
           <t>stimuli/ball/ball_11.jpg</t>
@@ -10578,19 +10578,19 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_49.jpg</t>
+          <t>stimuli/bread/bread_34.jpg</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
+          <t>hammer</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
           <t>bicycle</t>
         </is>
       </c>
-      <c r="J103" t="inlineStr">
-        <is>
-          <t>flower</t>
-        </is>
-      </c>
       <c r="K103" t="inlineStr">
         <is>
           <t>ball</t>
@@ -10598,7 +10598,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
@@ -10631,16 +10631,16 @@
         <v>12</v>
       </c>
       <c r="T103" t="n">
+        <v>7</v>
+      </c>
+      <c r="U103" t="n">
         <v>2</v>
-      </c>
-      <c r="U103" t="n">
-        <v>6</v>
       </c>
       <c r="V103" t="n">
         <v>1</v>
       </c>
       <c r="W103" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="104">
@@ -10662,7 +10662,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_36.jpg</t>
+          <t>stimuli/bicycle/bicycle_22.jpg</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -10677,12 +10677,12 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_34.jpg</t>
+          <t>stimuli/jacket/jacket_12.jpg</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>bicycle</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -10697,7 +10697,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>hand</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
@@ -10730,7 +10730,7 @@
         <v>13</v>
       </c>
       <c r="T104" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="U104" t="n">
         <v>14</v>
@@ -10739,7 +10739,7 @@
         <v>16</v>
       </c>
       <c r="W104" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="105">
